--- a/education_forms/035_child_safety_violation_notification--education_forms.xlsx
+++ b/education_forms/035_child_safety_violation_notification--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,8 +912,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -941,12 +941,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'teacher',_'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher', 'value': 'teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Parent', 'value': 'parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'staff_member',_'value':_'staff'}</t>
+          <t>staff_member</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Staff Member', 'value': 'staff'}</t>
+          <t>Staff Member</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'visitor',_'value':_'visitor'}</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Visitor', 'value': 'visitor'}</t>
+          <t>Visitor</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_supervision',_'value':_'supervision'}</t>
+          <t>lack_of_supervision</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of Supervision', 'value': 'supervision'}</t>
+          <t>Lack of Supervision</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'physical_hazard',_'value':_'hazard'}</t>
+          <t>physical_hazard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Physical Hazard', 'value': 'hazard'}</t>
+          <t>Physical Hazard</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'protocol_breach',_'value':_'protocol'}</t>
+          <t>protocol_breach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Protocol Breach', 'value': 'protocol'}</t>
+          <t>Protocol Breach</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'unsafe_equipment',_'value':_'equipment'}</t>
+          <t>unsafe_equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Unsafe Equipment', 'value': 'equipment'}</t>
+          <t>Unsafe Equipment</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
